--- a/B/chrVII:99176-198351_38_finemapping.xlsx
+++ b/B/chrVII:99176-198351_38_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3922" uniqueCount="3922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="3914">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -10751,19 +10751,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -11121,21 +11112,6 @@
   </si>
   <si>
     <t xml:space="preserve">YMR181C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -12216,48 +12192,42 @@
         <v>3575</v>
       </c>
       <c r="Z1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3576</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3577</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3578</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3579</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3580</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3581</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3582</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3583</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3585</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>3587</v>
+        <v>3584</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -12311,62 +12281,60 @@
         <v>197465</v>
       </c>
       <c r="U2" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V2" t="n">
         <v>432588</v>
       </c>
       <c r="W2" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3587</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.188423146967371</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0284942333876553</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3588</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="b">
+      <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>3592</v>
+      <c r="AH2" t="s">
+        <v>3589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>3593</v>
+        <v>3590</v>
       </c>
       <c r="D3" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E3" t="n">
         <v>124322</v>
@@ -12417,62 +12385,60 @@
         <v>139707</v>
       </c>
       <c r="U3" t="s">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="V3" t="n">
         <v>231281</v>
       </c>
       <c r="W3" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.207872094720444</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0380910009822107</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3595</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>3599</v>
+      <c r="AH3" t="s">
+        <v>3596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>3600</v>
+        <v>3597</v>
       </c>
       <c r="D4" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="E4" t="n">
         <v>145053</v>
@@ -12523,62 +12489,60 @@
         <v>154885</v>
       </c>
       <c r="U4" t="s">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="V4" t="n">
         <v>107256</v>
       </c>
       <c r="W4" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.128301883034946</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0254337391867237</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3601</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>3604</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3604</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>3605</v>
+      <c r="AH4" t="s">
+        <v>3602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="D5" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E5" t="n">
         <v>123533</v>
@@ -12629,62 +12593,60 @@
         <v>139707</v>
       </c>
       <c r="U5" t="s">
-        <v>3607</v>
+        <v>3604</v>
       </c>
       <c r="V5" t="n">
         <v>14957</v>
       </c>
       <c r="W5" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.268487736834917</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0590083649773277</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3605</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3605</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>3609</v>
+      <c r="AH5" t="s">
+        <v>3606</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>3610</v>
+        <v>3607</v>
       </c>
       <c r="D6" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="E6" t="n">
         <v>102109</v>
@@ -12735,62 +12697,60 @@
         <v>102109</v>
       </c>
       <c r="U6" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V6" t="n">
         <v>128512</v>
       </c>
       <c r="W6" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.684146733641696</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.182758864449217</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3588</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF6" t="n">
         <v>4</v>
       </c>
-      <c r="AI6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3612</v>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3609</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="D7" t="s">
-        <v>3614</v>
+        <v>3611</v>
       </c>
       <c r="E7" t="n">
         <v>145053</v>
@@ -12841,62 +12801,60 @@
         <v>153186</v>
       </c>
       <c r="U7" t="s">
-        <v>3615</v>
+        <v>3612</v>
       </c>
       <c r="V7" t="n">
         <v>93619</v>
       </c>
       <c r="W7" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.25641989922041</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0627436366389858</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3613</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>3616</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3616</v>
-      </c>
-      <c r="AH7" t="n">
+        <v>3613</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" t="b">
+      <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>3617</v>
+      <c r="AH7" t="s">
+        <v>3614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3618</v>
+        <v>3615</v>
       </c>
       <c r="D8" t="s">
-        <v>3619</v>
+        <v>3616</v>
       </c>
       <c r="E8" t="n">
         <v>175645</v>
@@ -12947,59 +12905,57 @@
         <v>175645</v>
       </c>
       <c r="U8" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="V8" t="n">
         <v>232285</v>
       </c>
       <c r="W8" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.035789445266195</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.00873805527543138</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3618</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>3618</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>3622</v>
+      <c r="AH8" t="s">
+        <v>3619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>3623</v>
+        <v>3620</v>
       </c>
       <c r="D9" t="s">
         <v>159</v>
@@ -13053,62 +13009,60 @@
         <v>191826</v>
       </c>
       <c r="U9" t="s">
-        <v>3624</v>
+        <v>3621</v>
       </c>
       <c r="V9" t="n">
         <v>326270</v>
       </c>
       <c r="W9" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.0313843399214784</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.00860096247848956</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3622</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3622</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" t="b">
+      <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>3626</v>
+      <c r="AH9" t="s">
+        <v>3623</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>3627</v>
+        <v>3624</v>
       </c>
       <c r="D10" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="E10" t="n">
         <v>124322</v>
@@ -13159,62 +13113,60 @@
         <v>159045</v>
       </c>
       <c r="U10" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V10" t="n">
         <v>829918</v>
       </c>
       <c r="W10" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.0854789658360806</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0251550649447854</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3588</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>3629</v>
+      <c r="AH10" t="s">
+        <v>3626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="D11" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E11" t="n">
         <v>123533</v>
@@ -13265,62 +13217,60 @@
         <v>139707</v>
       </c>
       <c r="U11" t="s">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="V11" t="n">
         <v>444686</v>
       </c>
       <c r="W11" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.0372447412104159</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0107788242631085</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3595</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>3631</v>
+      <c r="AH11" t="s">
+        <v>3628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>3632</v>
+        <v>3629</v>
       </c>
       <c r="D12" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="E12" t="n">
         <v>123533</v>
@@ -13371,62 +13321,60 @@
         <v>159045</v>
       </c>
       <c r="U12" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="V12" t="n">
         <v>63942</v>
       </c>
       <c r="W12" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.0933561719045099</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0275081726249092</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3618</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>3618</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" t="b">
+      <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>3633</v>
+      <c r="AH12" t="s">
+        <v>3630</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>3634</v>
+        <v>3631</v>
       </c>
       <c r="D13" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E13" t="n">
         <v>123533</v>
@@ -13477,62 +13425,60 @@
         <v>139707</v>
       </c>
       <c r="U13" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="V13" t="n">
         <v>229171</v>
       </c>
       <c r="W13" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.135887294555063</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0422112338898015</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3633</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3633</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>3637</v>
+      <c r="AH13" t="s">
+        <v>3634</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>3638</v>
+        <v>3635</v>
       </c>
       <c r="D14" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E14" t="n">
         <v>123533</v>
@@ -13583,62 +13529,60 @@
         <v>139707</v>
       </c>
       <c r="U14" t="s">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="V14" t="n">
         <v>159473</v>
       </c>
       <c r="W14" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.0604713727920993</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0188807089767743</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3595</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" t="b">
+      <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>3639</v>
+      <c r="AH14" t="s">
+        <v>3636</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>3640</v>
+        <v>3637</v>
       </c>
       <c r="D15" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E15" t="n">
         <v>117824</v>
@@ -13689,62 +13633,60 @@
         <v>145053</v>
       </c>
       <c r="U15" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V15" t="n">
         <v>700594</v>
       </c>
       <c r="W15" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.0329990551564825</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0105114019239365</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3588</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>3642</v>
+      <c r="AH15" t="s">
+        <v>3639</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>3643</v>
+        <v>3640</v>
       </c>
       <c r="D16" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E16" t="n">
         <v>124322</v>
@@ -13795,62 +13737,60 @@
         <v>145053</v>
       </c>
       <c r="U16" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V16" t="n">
         <v>550464</v>
       </c>
       <c r="W16" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.114658864553368</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0361880949869626</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3588</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>3644</v>
+      <c r="AH16" t="s">
+        <v>3641</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>3645</v>
+        <v>3642</v>
       </c>
       <c r="D17" t="s">
-        <v>3619</v>
+        <v>3616</v>
       </c>
       <c r="E17" t="n">
         <v>145053</v>
@@ -13901,62 +13841,60 @@
         <v>175645</v>
       </c>
       <c r="U17" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V17" t="n">
         <v>861306</v>
       </c>
       <c r="W17" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.16504039515348</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0520604294284416</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3588</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>3646</v>
+      <c r="AH17" t="s">
+        <v>3643</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>3647</v>
+        <v>3644</v>
       </c>
       <c r="D18" t="s">
-        <v>3648</v>
+        <v>3645</v>
       </c>
       <c r="E18" t="n">
         <v>153186</v>
@@ -14007,62 +13945,60 @@
         <v>184067</v>
       </c>
       <c r="U18" t="s">
-        <v>3624</v>
+        <v>3621</v>
       </c>
       <c r="V18" t="n">
         <v>164797</v>
       </c>
       <c r="W18" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.178017687016735</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.057589176784246</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3622</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3622</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>3649</v>
+      <c r="AH18" t="s">
+        <v>3646</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>3650</v>
+        <v>3647</v>
       </c>
       <c r="D19" t="s">
-        <v>3651</v>
+        <v>3648</v>
       </c>
       <c r="E19" t="n">
         <v>81639</v>
@@ -14113,62 +14049,60 @@
         <v>117824</v>
       </c>
       <c r="U19" t="s">
-        <v>3652</v>
+        <v>3649</v>
       </c>
       <c r="V19" t="n">
         <v>292066</v>
       </c>
       <c r="W19" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.2198246336115</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0836109022040179</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3650</v>
       </c>
       <c r="AD19" t="s">
         <v>19</v>
       </c>
       <c r="AE19" t="s">
-        <v>3653</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3653</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3650</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2</v>
       </c>
-      <c r="AI19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>3654</v>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>3651</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>3655</v>
+        <v>3652</v>
       </c>
       <c r="D20" t="s">
-        <v>3656</v>
+        <v>3653</v>
       </c>
       <c r="E20" t="n">
         <v>153186</v>
@@ -14219,62 +14153,60 @@
         <v>182104</v>
       </c>
       <c r="U20" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V20" t="n">
         <v>259594</v>
       </c>
       <c r="W20" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.0669069616665893</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0217678372484586</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3588</v>
       </c>
       <c r="AD20" t="s">
         <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3657</v>
+      <c r="AH20" t="s">
+        <v>3654</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>3658</v>
+        <v>3655</v>
       </c>
       <c r="D21" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E21" t="n">
         <v>123533</v>
@@ -14325,62 +14257,60 @@
         <v>145053</v>
       </c>
       <c r="U21" t="s">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="V21" t="n">
         <v>79907</v>
       </c>
       <c r="W21" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.111895476041529</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0452620772196464</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3657</v>
       </c>
       <c r="AD21" t="s">
         <v>19</v>
       </c>
       <c r="AE21" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>3657</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2</v>
       </c>
-      <c r="AI21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>3661</v>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>3658</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>3662</v>
+        <v>3659</v>
       </c>
       <c r="D22" t="s">
-        <v>3619</v>
+        <v>3616</v>
       </c>
       <c r="E22" t="n">
         <v>159045</v>
@@ -14431,62 +14361,60 @@
         <v>175645</v>
       </c>
       <c r="U22" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="V22" t="n">
         <v>837871</v>
       </c>
       <c r="W22" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0533764933670391</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0190741475223126</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3618</v>
       </c>
       <c r="AD22" t="s">
         <v>19</v>
       </c>
       <c r="AE22" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3618</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>3663</v>
+      <c r="AH22" t="s">
+        <v>3660</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>3664</v>
+        <v>3661</v>
       </c>
       <c r="D23" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="E23" t="n">
         <v>153186</v>
@@ -14537,62 +14465,60 @@
         <v>154885</v>
       </c>
       <c r="U23" t="s">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="V23" t="n">
         <v>127299</v>
       </c>
       <c r="W23" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.243644740303398</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0826608449660583</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3657</v>
       </c>
       <c r="AD23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3657</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3665</v>
+      <c r="AH23" t="s">
+        <v>3662</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>3666</v>
+        <v>3663</v>
       </c>
       <c r="D24" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="E24" t="n">
         <v>145053</v>
@@ -14643,62 +14569,60 @@
         <v>159045</v>
       </c>
       <c r="U24" t="s">
-        <v>3624</v>
+        <v>3621</v>
       </c>
       <c r="V24" t="n">
         <v>166544</v>
       </c>
       <c r="W24" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.102551786074185</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0355563695754742</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3622</v>
       </c>
       <c r="AD24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3625</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>3622</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" t="b">
+      <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>3667</v>
+      <c r="AH24" t="s">
+        <v>3664</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>3668</v>
+        <v>3665</v>
       </c>
       <c r="D25" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="E25" t="n">
         <v>145053</v>
@@ -14749,62 +14673,60 @@
         <v>159045</v>
       </c>
       <c r="U25" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V25" t="n">
         <v>82505</v>
       </c>
       <c r="W25" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.193787298562944</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.07775420056774</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3588</v>
       </c>
       <c r="AD25" t="s">
         <v>19</v>
       </c>
       <c r="AE25" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF25" t="n">
         <v>3</v>
       </c>
-      <c r="AI25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>3668</v>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>3665</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>3669</v>
+        <v>3666</v>
       </c>
       <c r="D26" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E26" t="n">
         <v>123533</v>
@@ -14855,62 +14777,60 @@
         <v>145053</v>
       </c>
       <c r="U26" t="s">
-        <v>3607</v>
+        <v>3604</v>
       </c>
       <c r="V26" t="n">
         <v>475769</v>
       </c>
       <c r="W26" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.131420917556333</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0449887952767095</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3605</v>
       </c>
       <c r="AD26" t="s">
         <v>19</v>
       </c>
       <c r="AE26" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AH26" t="n">
+        <v>3605</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="b">
+      <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>3670</v>
+      <c r="AH26" t="s">
+        <v>3667</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>3671</v>
+        <v>3668</v>
       </c>
       <c r="D27" t="s">
-        <v>3656</v>
+        <v>3653</v>
       </c>
       <c r="E27" t="n">
         <v>153186</v>
@@ -14961,62 +14881,60 @@
         <v>182104</v>
       </c>
       <c r="U27" t="s">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="V27" t="n">
         <v>488789</v>
       </c>
       <c r="W27" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.0933469632239258</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.033445883885546</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3657</v>
       </c>
       <c r="AD27" t="s">
         <v>19</v>
       </c>
       <c r="AE27" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>3657</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>3672</v>
+      <c r="AH27" t="s">
+        <v>3669</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>3673</v>
+        <v>3670</v>
       </c>
       <c r="D28" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E28" t="n">
         <v>124322</v>
@@ -15067,62 +14985,60 @@
         <v>145053</v>
       </c>
       <c r="U28" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="V28" t="n">
         <v>264324</v>
       </c>
       <c r="W28" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-0.101129706168073</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0376135920060342</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>3633</v>
       </c>
       <c r="AD28" t="s">
         <v>19</v>
       </c>
       <c r="AE28" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AH28" t="n">
+        <v>3633</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" t="b">
+      <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>3674</v>
+      <c r="AH28" t="s">
+        <v>3671</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>3675</v>
+        <v>3672</v>
       </c>
       <c r="D29" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="E29" t="n">
         <v>102109</v>
@@ -15173,62 +15089,60 @@
         <v>139707</v>
       </c>
       <c r="U29" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="V29" t="n">
         <v>95445</v>
       </c>
       <c r="W29" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.0751095348894015</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0278342760912141</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>3618</v>
       </c>
       <c r="AD29" t="s">
         <v>19</v>
       </c>
       <c r="AE29" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>3618</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" t="b">
+      <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>3676</v>
+      <c r="AH29" t="s">
+        <v>3673</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>3677</v>
+        <v>3674</v>
       </c>
       <c r="D30" t="s">
-        <v>3614</v>
+        <v>3611</v>
       </c>
       <c r="E30" t="n">
         <v>139707</v>
@@ -15279,59 +15193,57 @@
         <v>153186</v>
       </c>
       <c r="U30" t="s">
-        <v>3607</v>
+        <v>3604</v>
       </c>
       <c r="V30" t="n">
         <v>70624</v>
       </c>
       <c r="W30" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.168125582449792</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0587195799203855</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>3605</v>
       </c>
       <c r="AD30" t="s">
         <v>19</v>
       </c>
       <c r="AE30" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>3605</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>3678</v>
+      <c r="AH30" t="s">
+        <v>3675</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>3679</v>
+        <v>3676</v>
       </c>
       <c r="D31" t="s">
         <v>124</v>
@@ -15385,59 +15297,57 @@
         <v>123533</v>
       </c>
       <c r="U31" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="V31" t="n">
         <v>921860</v>
       </c>
       <c r="W31" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z31" t="n">
         <v>-0.18148065233789</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0626864022203716</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>3588</v>
       </c>
       <c r="AD31" t="s">
         <v>19</v>
       </c>
       <c r="AE31" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>3591</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>3588</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>3680</v>
+      <c r="AH31" t="s">
+        <v>3677</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>3681</v>
+        <v>3678</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -15491,62 +15401,60 @@
         <v>197465</v>
       </c>
       <c r="U32" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="V32" t="n">
         <v>579458</v>
       </c>
       <c r="W32" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>3587</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.0195029164085018</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0100213616837268</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>3633</v>
       </c>
       <c r="AD32" t="s">
         <v>19</v>
       </c>
       <c r="AE32" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>3633</v>
+      </c>
+      <c r="AF32" t="n">
         <v>3</v>
       </c>
-      <c r="AI32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>3682</v>
+      <c r="AG32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>3679</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>3683</v>
+        <v>3680</v>
       </c>
       <c r="D33" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="E33" t="n">
         <v>123533</v>
@@ -15597,62 +15505,60 @@
         <v>145053</v>
       </c>
       <c r="U33" t="s">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="V33" t="n">
         <v>657264</v>
       </c>
       <c r="W33" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-0.15930487605276</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0567685265395094</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>3595</v>
       </c>
       <c r="AD33" t="s">
         <v>19</v>
       </c>
       <c r="AE33" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>3598</v>
-      </c>
-      <c r="AH33" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" t="b">
+      <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>3684</v>
+      <c r="AH33" t="s">
+        <v>3681</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>3685</v>
+        <v>3682</v>
       </c>
       <c r="D34" t="s">
-        <v>3648</v>
+        <v>3645</v>
       </c>
       <c r="E34" t="n">
         <v>145053</v>
@@ -15703,62 +15609,60 @@
         <v>184067</v>
       </c>
       <c r="U34" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="V34" t="n">
         <v>971688</v>
       </c>
       <c r="W34" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z34" t="n">
         <v>-0.138935792478141</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0505949737040682</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>3633</v>
       </c>
       <c r="AD34" t="s">
         <v>19</v>
       </c>
       <c r="AE34" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AH34" t="n">
+        <v>3633</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" t="b">
+      <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>3686</v>
+      <c r="AH34" t="s">
+        <v>3683</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>3687</v>
+        <v>3684</v>
       </c>
       <c r="D35" t="s">
-        <v>3688</v>
+        <v>3685</v>
       </c>
       <c r="E35" t="n">
         <v>159045</v>
@@ -15809,62 +15713,60 @@
         <v>187246</v>
       </c>
       <c r="U35" t="s">
-        <v>3615</v>
+        <v>3612</v>
       </c>
       <c r="V35" t="n">
         <v>423689</v>
       </c>
       <c r="W35" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.0827098856054283</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.037768033608025</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>3613</v>
       </c>
       <c r="AD35" t="s">
         <v>19</v>
       </c>
       <c r="AE35" t="s">
-        <v>3616</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>3616</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>3689</v>
+        <v>3613</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>3686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>3690</v>
+        <v>3687</v>
       </c>
       <c r="D36" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="E36" t="n">
         <v>124322</v>
@@ -15915,62 +15817,60 @@
         <v>159045</v>
       </c>
       <c r="U36" t="s">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="V36" t="n">
         <v>84379</v>
       </c>
       <c r="W36" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z36" t="n">
         <v>-0.313218479616335</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.135631255988831</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>3657</v>
       </c>
       <c r="AD36" t="s">
         <v>19</v>
       </c>
       <c r="AE36" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>3660</v>
-      </c>
-      <c r="AH36" t="n">
+        <v>3657</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" t="b">
+      <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>3691</v>
+      <c r="AH36" t="s">
+        <v>3688</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>3692</v>
+        <v>3689</v>
       </c>
       <c r="D37" t="s">
-        <v>3648</v>
+        <v>3645</v>
       </c>
       <c r="E37" t="n">
         <v>175645</v>
@@ -16021,59 +15921,57 @@
         <v>184067</v>
       </c>
       <c r="U37" t="s">
-        <v>3693</v>
+        <v>3690</v>
       </c>
       <c r="V37" t="n">
         <v>302680</v>
       </c>
       <c r="W37" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.0221542005375678</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.00994912761737997</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>3691</v>
       </c>
       <c r="AD37" t="s">
         <v>19</v>
       </c>
       <c r="AE37" t="s">
-        <v>3694</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>3694</v>
-      </c>
-      <c r="AH37" t="n">
+        <v>3691</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="b">
+      <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>3695</v>
+      <c r="AH37" t="s">
+        <v>3692</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>3696</v>
+        <v>3693</v>
       </c>
       <c r="D38" t="s">
         <v>124</v>
@@ -16127,62 +16025,60 @@
         <v>123533</v>
       </c>
       <c r="U38" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="V38" t="n">
         <v>806621</v>
       </c>
       <c r="W38" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>3597</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-0.203623894066592</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.075752526857483</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>3633</v>
       </c>
       <c r="AD38" t="s">
         <v>19</v>
       </c>
       <c r="AE38" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>3636</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>3633</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" t="b">
+      <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>3697</v>
+      <c r="AH38" t="s">
+        <v>3694</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>3586</v>
+        <v>3583</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>3698</v>
+        <v>3695</v>
       </c>
       <c r="D39" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="E39" t="n">
         <v>124322</v>
@@ -16233,48 +16129,46 @@
         <v>154885</v>
       </c>
       <c r="U39" t="s">
-        <v>3607</v>
+        <v>3604</v>
       </c>
       <c r="V39" t="n">
         <v>623329</v>
       </c>
       <c r="W39" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>3600</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-0.14662746990826</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.0625994969848807</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>3605</v>
       </c>
       <c r="AD39" t="s">
         <v>19</v>
       </c>
       <c r="AE39" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>3608</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>3605</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" t="b">
+      <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>3698</v>
+      <c r="AH39" t="s">
+        <v>3695</v>
       </c>
     </row>
   </sheetData>
@@ -16353,37 +16247,28 @@
         <v>3572</v>
       </c>
       <c r="V1" t="s">
-        <v>3699</v>
+        <v>119</v>
       </c>
       <c r="W1" t="s">
-        <v>3700</v>
+        <v>3576</v>
       </c>
       <c r="X1" t="s">
-        <v>3701</v>
+        <v>3577</v>
       </c>
       <c r="Y1" t="s">
-        <v>3702</v>
+        <v>3578</v>
       </c>
       <c r="Z1" t="s">
-        <v>3703</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="AB1" t="s">
-        <v>3581</v>
+        <v>3696</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3582</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3704</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3585</v>
       </c>
     </row>
     <row r="2">
@@ -16394,7 +16279,7 @@
         <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="D2" t="n">
         <v>154885</v>
@@ -16451,36 +16336,27 @@
         <v>157906</v>
       </c>
       <c r="V2" t="n">
-        <v>11.0764546460652</v>
+        <v>0.391598610448108</v>
       </c>
       <c r="W2" t="n">
-        <v>5.53173450280764</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6.87898606406312</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.74517958636885</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6.51051996548445</v>
+        <v>0.0504466601019219</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
         <v>94</v>
       </c>
     </row>
@@ -16489,10 +16365,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
       <c r="C3" t="s">
-        <v>3706</v>
+        <v>3698</v>
       </c>
       <c r="D3" t="n">
         <v>199203</v>
@@ -16549,37 +16425,28 @@
         <v>199081</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.1378968530089</v>
+        <v>-0.296358928685863</v>
       </c>
       <c r="W3" t="n">
-        <v>-4.36772907094632</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-3.48318379348308</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-3.70311946815597</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-7.53222910542795</v>
+        <v>0.0448877547332957</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3707</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="4">
@@ -16587,7 +16454,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="C4" t="s">
         <v>159</v>
@@ -16647,37 +16514,28 @@
         <v>150996</v>
       </c>
       <c r="V4" t="n">
-        <v>-7.99596817502994</v>
+        <v>-0.267803122989365</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.2411685301716</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.06311678204754</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3.2613038626049</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-1.03372505170346</v>
+        <v>0.0548870630444115</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="5">
@@ -16685,10 +16543,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="C5" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="D5" t="n">
         <v>139707</v>
@@ -16745,37 +16603,28 @@
         <v>139571</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.27553093836565</v>
+        <v>-0.368216534572581</v>
       </c>
       <c r="W5" t="n">
-        <v>-3.57449064357103</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-3.23791608242569</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-3.76241902305122</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-4.11436774763632</v>
+        <v>0.0801773415522978</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="6">
@@ -16783,10 +16632,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
       <c r="C6" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="D6" t="n">
         <v>123533</v>
@@ -16843,37 +16692,28 @@
         <v>144808</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.78118107893087</v>
+        <v>-0.106783313577947</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.36938411733983</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.94677279633471</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.63016555876609</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2.0491827367426</v>
+        <v>0.0299345138979863</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="7">
@@ -16881,10 +16721,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="C7" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="D7" t="n">
         <v>209977</v>
@@ -16941,37 +16781,28 @@
         <v>209006</v>
       </c>
       <c r="V7" t="n">
-        <v>5.60165737161673</v>
+        <v>0.221654048800971</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23289748395158</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.18117983179767</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.85481110964871</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.95714873969816</v>
+        <v>0.0673543873955874</v>
+      </c>
+      <c r="X7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" t="s">
-        <v>19</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3715</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="8">
@@ -16979,10 +16810,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="C8" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="D8" t="n">
         <v>153186</v>
@@ -17039,37 +16870,28 @@
         <v>153047</v>
       </c>
       <c r="V8" t="n">
-        <v>2.43283128088813</v>
+        <v>0.325575174896804</v>
       </c>
       <c r="W8" t="n">
-        <v>3.58102033682081</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.69493026247708</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>4.09643883324014</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.27307244523901</v>
+        <v>0.109465205575887</v>
+      </c>
+      <c r="X8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
         <v>19</v>
       </c>
-      <c r="AB8" t="s">
-        <v>19</v>
+      <c r="AB8" t="n">
+        <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="9">
@@ -17077,10 +16899,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
       <c r="C9" t="s">
-        <v>3651</v>
+        <v>3648</v>
       </c>
       <c r="D9" t="n">
         <v>102109</v>
@@ -17137,37 +16959,28 @@
         <v>116059</v>
       </c>
       <c r="V9" t="n">
-        <v>3.90469480046378</v>
+        <v>0.0952740837205218</v>
       </c>
       <c r="W9" t="n">
-        <v>2.00478569779195</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.95121228743895</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.74316593699059</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.933932516841235</v>
+        <v>0.0351807990975777</v>
+      </c>
+      <c r="X9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>19</v>
       </c>
       <c r="AA9" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" t="s">
-        <v>19</v>
+      <c r="AB9" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3718</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="10">
@@ -17175,10 +16988,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>3719</v>
+        <v>3711</v>
       </c>
       <c r="C10" t="s">
-        <v>3688</v>
+        <v>3685</v>
       </c>
       <c r="D10" t="n">
         <v>175645</v>
@@ -17235,37 +17048,28 @@
         <v>186059</v>
       </c>
       <c r="V10" t="n">
-        <v>2.85605269126066</v>
+        <v>0.17901409484074</v>
       </c>
       <c r="W10" t="n">
-        <v>3.10360638952548</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.77830814377145</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.51707090959977</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.858598951955727</v>
+        <v>0.0741954358586929</v>
+      </c>
+      <c r="X10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>19</v>
       </c>
       <c r="AA10" t="s">
         <v>19</v>
       </c>
-      <c r="AB10" t="s">
-        <v>19</v>
+      <c r="AB10" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3720</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="11">
@@ -17273,10 +17077,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>3721</v>
+        <v>3713</v>
       </c>
       <c r="C11" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="D11" t="n">
         <v>94647</v>
@@ -17333,37 +17137,28 @@
         <v>102423</v>
       </c>
       <c r="V11" t="n">
-        <v>2.06935745509387</v>
+        <v>0.131659224365432</v>
       </c>
       <c r="W11" t="n">
-        <v>2.23387405835121</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.65525145251752</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.59859209345957</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.87389359951384</v>
+        <v>0.0568902811686573</v>
+      </c>
+      <c r="X11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>19</v>
       </c>
       <c r="AA11" t="s">
         <v>19</v>
       </c>
-      <c r="AB11" t="s">
-        <v>19</v>
+      <c r="AB11" t="n">
+        <v>0.00082135523613963</v>
       </c>
       <c r="AC11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.00082135523613963</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3722</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="12">
@@ -17371,10 +17166,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>3723</v>
+        <v>3715</v>
       </c>
       <c r="C12" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="D12" t="n">
         <v>191826</v>
@@ -17431,37 +17226,28 @@
         <v>174545</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.3437772973679</v>
+        <v>-0.21747750488962</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.23383715582044</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.200506146232763</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.0858417648334459</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-2.5646438284498</v>
+        <v>0.106326399352703</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>19</v>
       </c>
       <c r="AA12" t="s">
         <v>19</v>
       </c>
-      <c r="AB12" t="s">
-        <v>19</v>
+      <c r="AB12" t="n">
+        <v>0.00141342756183746</v>
       </c>
       <c r="AC12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.00141342756183746</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3724</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="13">
@@ -17469,10 +17255,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="C13" t="s">
-        <v>3619</v>
+        <v>3616</v>
       </c>
       <c r="D13" t="n">
         <v>153186</v>
@@ -17529,37 +17315,28 @@
         <v>171295</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36396329238599</v>
+        <v>0.216760220409806</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91326166061391</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.911101029458134</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.23277875510617</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.31034399033499</v>
+        <v>0.125890446824811</v>
+      </c>
+      <c r="X13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>19</v>
       </c>
       <c r="AA13" t="s">
         <v>19</v>
       </c>
-      <c r="AB13" t="s">
-        <v>19</v>
+      <c r="AB13" t="n">
+        <v>0.00201680672268908</v>
       </c>
       <c r="AC13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.00201680672268908</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="14">
@@ -17567,10 +17344,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="C14" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="D14" t="n">
         <v>139707</v>
@@ -17627,37 +17404,28 @@
         <v>148704</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.91334820829596</v>
+        <v>-0.60735459776685</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.225479338967985</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.30648397139651</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.187481215175066</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-2.65085558990121</v>
+        <v>0.296612249203908</v>
+      </c>
+      <c r="X14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>19</v>
       </c>
       <c r="AA14" t="s">
         <v>19</v>
       </c>
-      <c r="AB14" t="s">
-        <v>19</v>
+      <c r="AB14" t="n">
+        <v>0.00280373831775701</v>
       </c>
       <c r="AC14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.00280373831775701</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="15">
@@ -17665,10 +17433,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="C15" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="D15" t="n">
         <v>117824</v>
@@ -17725,37 +17493,28 @@
         <v>160065</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3065045579512</v>
+        <v>0.332113997065017</v>
       </c>
       <c r="W15" t="n">
-        <v>2.10620322168652</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.65246971842296</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.89768516352</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.58120391360328</v>
+        <v>0.152555554243867</v>
+      </c>
+      <c r="X15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>19</v>
       </c>
       <c r="AA15" t="s">
         <v>19</v>
       </c>
-      <c r="AB15" t="s">
-        <v>19</v>
+      <c r="AB15" t="n">
+        <v>0.00301204819277108</v>
       </c>
       <c r="AC15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.00301204819277108</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3728</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="16">
@@ -17763,10 +17522,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>3729</v>
+        <v>3721</v>
       </c>
       <c r="C16" t="s">
-        <v>3614</v>
+        <v>3611</v>
       </c>
       <c r="D16" t="n">
         <v>139707</v>
@@ -17823,37 +17582,28 @@
         <v>163289</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0678216954468</v>
+        <v>-0.228965778727975</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.72158787348647</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.87482112307332</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-0.65149173568271</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-3.36764118241731</v>
+        <v>0.113809453935444</v>
+      </c>
+      <c r="X16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>19</v>
       </c>
       <c r="AA16" t="s">
         <v>19</v>
       </c>
-      <c r="AB16" t="s">
-        <v>19</v>
+      <c r="AB16" t="n">
+        <v>0.00408719346049046</v>
       </c>
       <c r="AC16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.00408719346049046</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3730</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="17">
@@ -17861,10 +17611,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="C17" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="D17" t="n">
         <v>81639</v>
@@ -17921,37 +17671,28 @@
         <v>131525</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.18928643321557</v>
+        <v>-0.062175255003181</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24703926763506</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.68338612771133</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-2.11643006818281</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-2.88859680250785</v>
+        <v>0.0531445993365048</v>
+      </c>
+      <c r="X17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>19</v>
       </c>
       <c r="AA17" t="s">
         <v>19</v>
       </c>
-      <c r="AB17" t="s">
-        <v>19</v>
+      <c r="AB17" t="n">
+        <v>0.00459459459459459</v>
       </c>
       <c r="AC17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.00459459459459459</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3732</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="18">
@@ -17959,10 +17700,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>3733</v>
+        <v>3725</v>
       </c>
       <c r="C18" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="D18" t="n">
         <v>96763</v>
@@ -18019,37 +17760,28 @@
         <v>124698</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.13675327416239</v>
+        <v>-0.169669435787353</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.6860133342017</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.488998081246604</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-2.53575132890335</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-3.50418964843581</v>
+        <v>0.112917768088506</v>
+      </c>
+      <c r="X18" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>19</v>
       </c>
       <c r="AA18" t="s">
         <v>19</v>
       </c>
-      <c r="AB18" t="s">
-        <v>19</v>
+      <c r="AB18" t="n">
+        <v>0.00474255924087112</v>
       </c>
       <c r="AC18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.00474255924087112</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>3734</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="19">
@@ -18057,10 +17789,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>3735</v>
+        <v>3727</v>
       </c>
       <c r="C19" t="s">
-        <v>3736</v>
+        <v>3728</v>
       </c>
       <c r="D19" t="n">
         <v>267759</v>
@@ -18117,37 +17849,28 @@
         <v>98969</v>
       </c>
       <c r="V19" t="n">
-        <v>0.144110567987404</v>
+        <v>-0.0470698736254</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.99828887749978</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.41861311339764</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-2.19383004719895</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-2.34944999988175</v>
+        <v>0.0543206642263586</v>
+      </c>
+      <c r="X19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>19</v>
       </c>
       <c r="AA19" t="s">
         <v>19</v>
       </c>
-      <c r="AB19" t="s">
-        <v>19</v>
+      <c r="AB19" t="n">
+        <v>0.00813810110974106</v>
       </c>
       <c r="AC19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.00813810110974106</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="20">
@@ -18155,7 +17878,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>3738</v>
+        <v>3730</v>
       </c>
       <c r="C20" t="s">
         <v>137</v>
@@ -18215,37 +17938,28 @@
         <v>129883</v>
       </c>
       <c r="V20" t="n">
-        <v>4.04057793600115</v>
+        <v>0.109884259706745</v>
       </c>
       <c r="W20" t="n">
-        <v>0.359719400453825</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.993888052425181</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.742512145073643</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.968296570669754</v>
+        <v>0.071846966208017</v>
+      </c>
+      <c r="X20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>19</v>
       </c>
       <c r="AA20" t="s">
         <v>19</v>
       </c>
-      <c r="AB20" t="s">
-        <v>19</v>
+      <c r="AB20" t="n">
+        <v>0.012738651008858</v>
       </c>
       <c r="AC20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.012738651008858</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>3739</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
@@ -18253,10 +17967,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="C21" t="s">
-        <v>3651</v>
+        <v>3648</v>
       </c>
       <c r="D21" t="n">
         <v>102109</v>
@@ -18313,37 +18027,28 @@
         <v>111580</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.94434377084306</v>
+        <v>-0.444773116088566</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.46733513761357</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.0946210707723785</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-1.56191081812633</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.0124005301130894</v>
+        <v>0.299997510571531</v>
+      </c>
+      <c r="X21" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>19</v>
       </c>
       <c r="AA21" t="s">
         <v>19</v>
       </c>
-      <c r="AB21" t="s">
-        <v>19</v>
+      <c r="AB21" t="n">
+        <v>0.012766868198557</v>
       </c>
       <c r="AC21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.012766868198557</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="22">
@@ -18351,10 +18056,10 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="C22" t="s">
-        <v>3742</v>
+        <v>3734</v>
       </c>
       <c r="D22" t="n">
         <v>694539</v>
@@ -18411,37 +18116,28 @@
         <v>149460</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.15120483922666</v>
+        <v>0.010136843882229</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.654454877787607</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.49402732320656</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-1.02033442711921</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.72174533562511</v>
+        <v>0.0404927236450955</v>
+      </c>
+      <c r="X22" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>19</v>
       </c>
       <c r="AA22" t="s">
         <v>19</v>
       </c>
-      <c r="AB22" t="s">
-        <v>19</v>
+      <c r="AB22" t="n">
+        <v>0.0139059467917758</v>
       </c>
       <c r="AC22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.0139059467917758</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>3743</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="23">
@@ -18449,10 +18145,10 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>3744</v>
+        <v>3736</v>
       </c>
       <c r="C23" t="s">
-        <v>3745</v>
+        <v>3737</v>
       </c>
       <c r="D23" t="n">
         <v>369074</v>
@@ -18509,37 +18205,28 @@
         <v>167352</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34838559000007</v>
+        <v>0.0180795437059078</v>
       </c>
       <c r="W23" t="n">
-        <v>-2.4636430896566</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-1.12251808798293</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.69181398196565</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-0.841994262290806</v>
+        <v>0.109940169772506</v>
+      </c>
+      <c r="X23" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>19</v>
       </c>
       <c r="AA23" t="s">
         <v>19</v>
       </c>
-      <c r="AB23" t="s">
-        <v>19</v>
+      <c r="AB23" t="n">
+        <v>0.0214513892936689</v>
       </c>
       <c r="AC23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.0214513892936689</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>3746</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="24">
@@ -18547,10 +18234,10 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>3747</v>
+        <v>3739</v>
       </c>
       <c r="C24" t="s">
-        <v>3748</v>
+        <v>3740</v>
       </c>
       <c r="D24" t="n">
         <v>175645</v>
@@ -18607,37 +18294,28 @@
         <v>148109</v>
       </c>
       <c r="V24" t="n">
-        <v>3.61318928510016</v>
+        <v>0.0112218289621511</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.826200860270113</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-1.21279445856445</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.17630149162154</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.781178288519502</v>
+        <v>0.00897054585850044</v>
+      </c>
+      <c r="X24" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>19</v>
       </c>
       <c r="AA24" t="s">
         <v>19</v>
       </c>
-      <c r="AB24" t="s">
-        <v>19</v>
+      <c r="AB24" t="n">
+        <v>0.0218467044848075</v>
       </c>
       <c r="AC24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.0218467044848075</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>3749</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="25">
@@ -18645,10 +18323,10 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>3750</v>
+        <v>3742</v>
       </c>
       <c r="C25" t="s">
-        <v>3751</v>
+        <v>3743</v>
       </c>
       <c r="D25" t="n">
         <v>641544</v>
@@ -18705,37 +18383,28 @@
         <v>112417</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.564626756885</v>
+        <v>-0.0974164759038142</v>
       </c>
       <c r="W25" t="n">
-        <v>0.671981381999397</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.935462268557347</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-2.70117071990744</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-2.37480125607011</v>
+        <v>0.0808003568782444</v>
+      </c>
+      <c r="X25" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>19</v>
       </c>
       <c r="AA25" t="s">
         <v>19</v>
       </c>
-      <c r="AB25" t="s">
-        <v>19</v>
+      <c r="AB25" t="n">
+        <v>0.0247771461154355</v>
       </c>
       <c r="AC25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.0247771461154355</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>3752</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="26">
@@ -18743,10 +18412,10 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>3753</v>
+        <v>3745</v>
       </c>
       <c r="C26" t="s">
-        <v>3754</v>
+        <v>3746</v>
       </c>
       <c r="D26" t="n">
         <v>81639</v>
@@ -18803,37 +18472,28 @@
         <v>175407</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.37971896749972</v>
+        <v>-0.0442750963048304</v>
       </c>
       <c r="W26" t="n">
-        <v>1.43404460691339</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-1.01244578039044</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29473601435532</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-0.630168498298029</v>
+        <v>0.0547973973256621</v>
+      </c>
+      <c r="X26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>19</v>
       </c>
       <c r="AA26" t="s">
         <v>19</v>
       </c>
-      <c r="AB26" t="s">
-        <v>19</v>
+      <c r="AB26" t="n">
+        <v>0.0262933538456039</v>
       </c>
       <c r="AC26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.0262933538456039</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>3755</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="27">
@@ -18841,10 +18501,10 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>3756</v>
+        <v>3748</v>
       </c>
       <c r="C27" t="s">
-        <v>3757</v>
+        <v>3749</v>
       </c>
       <c r="D27" t="n">
         <v>197465</v>
@@ -18901,37 +18561,28 @@
         <v>210416</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.43134511725077</v>
+        <v>-0.123015886937881</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.01552916914448</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-1.98449895256611</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>-0.437656837285909</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.04502567807962</v>
+        <v>0.0998185490703319</v>
+      </c>
+      <c r="X27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>19</v>
       </c>
       <c r="AA27" t="s">
         <v>19</v>
       </c>
-      <c r="AB27" t="s">
-        <v>19</v>
+      <c r="AB27" t="n">
+        <v>0.0283749188145878</v>
       </c>
       <c r="AC27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.0283749188145878</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>3758</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="28">
@@ -18939,10 +18590,10 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>3759</v>
+        <v>3751</v>
       </c>
       <c r="C28" t="s">
-        <v>3651</v>
+        <v>3648</v>
       </c>
       <c r="D28" t="n">
         <v>73336</v>
@@ -18999,37 +18650,28 @@
         <v>108158</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.54824938545163</v>
+        <v>-0.336131235635237</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.62594063878805</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.640883084807684</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>-1.37913173627634</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.120217328172661</v>
+        <v>0.251838793587427</v>
+      </c>
+      <c r="X28" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>19</v>
       </c>
       <c r="AA28" t="s">
         <v>19</v>
       </c>
-      <c r="AB28" t="s">
-        <v>19</v>
+      <c r="AB28" t="n">
+        <v>0.0332038553392428</v>
       </c>
       <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0.0332038553392428</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>3760</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="29">
@@ -19037,10 +18679,10 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="C29" t="s">
-        <v>3762</v>
+        <v>3754</v>
       </c>
       <c r="D29" t="n">
         <v>859016</v>
@@ -19097,37 +18739,28 @@
         <v>142246</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.13630261361189</v>
+        <v>-0.0972664507006423</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.200636296921139</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.15219402988212</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>-1.18202412369684</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-0.157852996297545</v>
+        <v>0.238064781064326</v>
+      </c>
+      <c r="X29" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>19</v>
       </c>
       <c r="AA29" t="s">
         <v>19</v>
       </c>
-      <c r="AB29" t="s">
-        <v>19</v>
+      <c r="AB29" t="n">
+        <v>0.0365251904505361</v>
       </c>
       <c r="AC29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.0365251904505361</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>3763</v>
+        <v>3755</v>
       </c>
     </row>
   </sheetData>
@@ -19158,34 +18791,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>3764</v>
+        <v>3756</v>
       </c>
       <c r="G1" t="s">
         <v>2110</v>
       </c>
       <c r="H1" t="s">
-        <v>3765</v>
+        <v>3757</v>
       </c>
       <c r="I1" t="s">
-        <v>3766</v>
+        <v>3758</v>
       </c>
       <c r="J1" t="s">
         <v>2113</v>
       </c>
       <c r="K1" t="s">
-        <v>3767</v>
+        <v>3759</v>
       </c>
       <c r="L1" t="s">
-        <v>3768</v>
+        <v>3760</v>
       </c>
       <c r="M1" t="s">
-        <v>3769</v>
+        <v>3761</v>
       </c>
       <c r="N1" t="s">
-        <v>3770</v>
+        <v>3762</v>
       </c>
       <c r="O1" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="P1" t="s">
         <v>3572</v>
@@ -19205,33 +18838,33 @@
         <v>1149</v>
       </c>
       <c r="E2" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F2" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G2" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3774</v>
+        <v>3766</v>
       </c>
       <c r="K2" t="s">
-        <v>3775</v>
+        <v>3767</v>
       </c>
       <c r="L2" t="s">
-        <v>3774</v>
+        <v>3766</v>
       </c>
       <c r="M2" t="s">
-        <v>3776</v>
+        <v>3768</v>
       </c>
       <c r="N2" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O2" t="s">
-        <v>3778</v>
+        <v>3770</v>
       </c>
       <c r="P2" t="n">
         <v>96432</v>
@@ -19251,33 +18884,33 @@
         <v>1248</v>
       </c>
       <c r="E3" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F3" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G3" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3779</v>
+        <v>3771</v>
       </c>
       <c r="K3" t="s">
-        <v>3780</v>
+        <v>3772</v>
       </c>
       <c r="L3" t="s">
-        <v>3779</v>
+        <v>3771</v>
       </c>
       <c r="M3" t="s">
-        <v>3781</v>
+        <v>3773</v>
       </c>
       <c r="N3" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O3" t="s">
-        <v>3782</v>
+        <v>3774</v>
       </c>
       <c r="P3" t="n">
         <v>97962</v>
@@ -19297,33 +18930,33 @@
         <v>3108</v>
       </c>
       <c r="E4" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F4" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G4" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3735</v>
+        <v>3727</v>
       </c>
       <c r="K4" t="s">
-        <v>3783</v>
+        <v>3775</v>
       </c>
       <c r="L4" t="s">
-        <v>3735</v>
+        <v>3727</v>
       </c>
       <c r="M4" t="s">
-        <v>3784</v>
+        <v>3776</v>
       </c>
       <c r="N4" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O4" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="P4" t="n">
         <v>100522</v>
@@ -19343,33 +18976,33 @@
         <v>4962</v>
       </c>
       <c r="E5" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F5" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G5" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3721</v>
+        <v>3713</v>
       </c>
       <c r="K5" t="s">
-        <v>3786</v>
+        <v>3778</v>
       </c>
       <c r="L5" t="s">
-        <v>3721</v>
+        <v>3713</v>
       </c>
       <c r="M5" t="s">
-        <v>3787</v>
+        <v>3779</v>
       </c>
       <c r="N5" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O5" t="s">
-        <v>3722</v>
+        <v>3714</v>
       </c>
       <c r="P5" t="n">
         <v>105024</v>
@@ -19389,33 +19022,33 @@
         <v>2247</v>
       </c>
       <c r="E6" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F6" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G6" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3759</v>
+        <v>3751</v>
       </c>
       <c r="K6" t="s">
-        <v>3788</v>
+        <v>3780</v>
       </c>
       <c r="L6" t="s">
-        <v>3759</v>
+        <v>3751</v>
       </c>
       <c r="M6" t="s">
-        <v>3789</v>
+        <v>3781</v>
       </c>
       <c r="N6" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O6" t="s">
-        <v>3760</v>
+        <v>3752</v>
       </c>
       <c r="P6" t="n">
         <v>109281</v>
@@ -19435,30 +19068,30 @@
         <v>306</v>
       </c>
       <c r="E7" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F7" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G7" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="K7" t="s">
-        <v>3790</v>
+        <v>3782</v>
       </c>
       <c r="L7" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="M7" t="s">
-        <v>3791</v>
+        <v>3783</v>
       </c>
       <c r="N7" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
@@ -19479,33 +19112,33 @@
         <v>2190</v>
       </c>
       <c r="E8" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F8" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G8" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3750</v>
+        <v>3742</v>
       </c>
       <c r="K8" t="s">
-        <v>3793</v>
+        <v>3785</v>
       </c>
       <c r="L8" t="s">
-        <v>3750</v>
+        <v>3742</v>
       </c>
       <c r="M8" t="s">
-        <v>3794</v>
+        <v>3786</v>
       </c>
       <c r="N8" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O8" t="s">
-        <v>3752</v>
+        <v>3744</v>
       </c>
       <c r="P8" t="n">
         <v>113570</v>
@@ -19525,33 +19158,33 @@
         <v>1503</v>
       </c>
       <c r="E9" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F9" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G9" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
       <c r="K9" t="s">
-        <v>3795</v>
+        <v>3787</v>
       </c>
       <c r="L9" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
       <c r="M9" t="s">
-        <v>3796</v>
+        <v>3788</v>
       </c>
       <c r="N9" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O9" t="s">
-        <v>3718</v>
+        <v>3710</v>
       </c>
       <c r="P9" t="n">
         <v>116810</v>
@@ -19571,33 +19204,33 @@
         <v>3054</v>
       </c>
       <c r="E10" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F10" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G10" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3797</v>
+        <v>3789</v>
       </c>
       <c r="K10" t="s">
-        <v>3798</v>
+        <v>3790</v>
       </c>
       <c r="L10" t="s">
-        <v>3797</v>
+        <v>3789</v>
       </c>
       <c r="M10" t="s">
-        <v>3799</v>
+        <v>3791</v>
       </c>
       <c r="N10" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O10" t="s">
-        <v>3800</v>
+        <v>3792</v>
       </c>
       <c r="P10" t="n">
         <v>119380</v>
@@ -19617,33 +19250,33 @@
         <v>612</v>
       </c>
       <c r="E11" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F11" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G11" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3801</v>
+        <v>3793</v>
       </c>
       <c r="K11" t="s">
-        <v>3802</v>
+        <v>3794</v>
       </c>
       <c r="L11" t="s">
-        <v>3801</v>
+        <v>3793</v>
       </c>
       <c r="M11" t="s">
-        <v>3803</v>
+        <v>3795</v>
       </c>
       <c r="N11" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O11" t="s">
-        <v>3804</v>
+        <v>3796</v>
       </c>
       <c r="P11" t="n">
         <v>123000</v>
@@ -19663,33 +19296,33 @@
         <v>708</v>
       </c>
       <c r="E12" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F12" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G12" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3805</v>
+        <v>3797</v>
       </c>
       <c r="K12" t="s">
-        <v>3806</v>
+        <v>3798</v>
       </c>
       <c r="L12" t="s">
-        <v>3805</v>
+        <v>3797</v>
       </c>
       <c r="M12" t="s">
-        <v>3807</v>
+        <v>3799</v>
       </c>
       <c r="N12" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O12" t="s">
-        <v>3808</v>
+        <v>3800</v>
       </c>
       <c r="P12" t="n">
         <v>123944</v>
@@ -19709,33 +19342,33 @@
         <v>4464</v>
       </c>
       <c r="E13" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F13" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G13" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3733</v>
+        <v>3725</v>
       </c>
       <c r="K13" t="s">
-        <v>3809</v>
+        <v>3801</v>
       </c>
       <c r="L13" t="s">
-        <v>3733</v>
+        <v>3725</v>
       </c>
       <c r="M13" t="s">
-        <v>3810</v>
+        <v>3802</v>
       </c>
       <c r="N13" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O13" t="s">
-        <v>3734</v>
+        <v>3726</v>
       </c>
       <c r="P13" t="n">
         <v>126930</v>
@@ -19755,33 +19388,33 @@
         <v>1287</v>
       </c>
       <c r="E14" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F14" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G14" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3738</v>
+        <v>3730</v>
       </c>
       <c r="K14" t="s">
-        <v>3811</v>
+        <v>3803</v>
       </c>
       <c r="L14" t="s">
-        <v>3738</v>
+        <v>3730</v>
       </c>
       <c r="M14" t="s">
-        <v>3812</v>
+        <v>3804</v>
       </c>
       <c r="N14" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O14" t="s">
-        <v>3739</v>
+        <v>3731</v>
       </c>
       <c r="P14" t="n">
         <v>130526</v>
@@ -19801,33 +19434,33 @@
         <v>8019</v>
       </c>
       <c r="E15" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F15" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G15" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="K15" t="s">
-        <v>3813</v>
+        <v>3805</v>
       </c>
       <c r="L15" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="M15" t="s">
-        <v>3814</v>
+        <v>3806</v>
       </c>
       <c r="N15" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O15" t="s">
-        <v>3732</v>
+        <v>3724</v>
       </c>
       <c r="P15" t="n">
         <v>135534</v>
@@ -19847,30 +19480,30 @@
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F16" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G16" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="K16" t="s">
-        <v>3815</v>
+        <v>3807</v>
       </c>
       <c r="L16" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="M16" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N16" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O16"/>
       <c r="P16" t="n">
@@ -19891,33 +19524,33 @@
         <v>1359</v>
       </c>
       <c r="E17" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F17" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G17" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3817</v>
+        <v>3809</v>
       </c>
       <c r="K17" t="s">
-        <v>3818</v>
+        <v>3810</v>
       </c>
       <c r="L17" t="s">
-        <v>3817</v>
+        <v>3809</v>
       </c>
       <c r="M17" t="s">
-        <v>3819</v>
+        <v>3811</v>
       </c>
       <c r="N17" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O17" t="s">
-        <v>3820</v>
+        <v>3812</v>
       </c>
       <c r="P17" t="n">
         <v>141047</v>
@@ -19937,30 +19570,30 @@
         <v>312</v>
       </c>
       <c r="E18" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F18" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G18" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3821</v>
+        <v>3813</v>
       </c>
       <c r="K18" t="s">
-        <v>3822</v>
+        <v>3814</v>
       </c>
       <c r="L18" t="s">
-        <v>3821</v>
+        <v>3813</v>
       </c>
       <c r="M18" t="s">
-        <v>3823</v>
+        <v>3815</v>
       </c>
       <c r="N18" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O18"/>
       <c r="P18" t="n">
@@ -19981,33 +19614,33 @@
         <v>1803</v>
       </c>
       <c r="E19" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F19" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G19" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="K19" t="s">
-        <v>3824</v>
+        <v>3816</v>
       </c>
       <c r="L19" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="M19" t="s">
-        <v>3825</v>
+        <v>3817</v>
       </c>
       <c r="N19" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O19" t="s">
-        <v>3763</v>
+        <v>3755</v>
       </c>
       <c r="P19" t="n">
         <v>143147</v>
@@ -20027,33 +19660,33 @@
         <v>390</v>
       </c>
       <c r="E20" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F20" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G20" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
       <c r="K20" t="s">
-        <v>3826</v>
+        <v>3818</v>
       </c>
       <c r="L20" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
       <c r="M20" t="s">
-        <v>3827</v>
+        <v>3819</v>
       </c>
       <c r="N20" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O20" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
       <c r="P20" t="n">
         <v>145002</v>
@@ -20073,33 +19706,33 @@
         <v>1581</v>
       </c>
       <c r="E21" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F21" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G21" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3828</v>
+        <v>3820</v>
       </c>
       <c r="K21" t="s">
-        <v>3829</v>
+        <v>3821</v>
       </c>
       <c r="L21" t="s">
-        <v>3828</v>
+        <v>3820</v>
       </c>
       <c r="M21" t="s">
-        <v>3830</v>
+        <v>3822</v>
       </c>
       <c r="N21" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O21" t="s">
-        <v>3831</v>
+        <v>3823</v>
       </c>
       <c r="P21" t="n">
         <v>146599</v>
@@ -20119,33 +19752,33 @@
         <v>738</v>
       </c>
       <c r="E22" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F22" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G22" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3747</v>
+        <v>3739</v>
       </c>
       <c r="K22" t="s">
-        <v>3832</v>
+        <v>3824</v>
       </c>
       <c r="L22" t="s">
-        <v>3747</v>
+        <v>3739</v>
       </c>
       <c r="M22" t="s">
-        <v>3833</v>
+        <v>3825</v>
       </c>
       <c r="N22" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O22" t="s">
-        <v>3749</v>
+        <v>3741</v>
       </c>
       <c r="P22" t="n">
         <v>148598</v>
@@ -20165,30 +19798,30 @@
         <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F23" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G23" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="K23" t="s">
-        <v>3834</v>
+        <v>3826</v>
       </c>
       <c r="L23" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="M23" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N23" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O23"/>
       <c r="P23" t="n">
@@ -20209,33 +19842,33 @@
         <v>822</v>
       </c>
       <c r="E24" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F24" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G24" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="K24" t="s">
-        <v>3835</v>
+        <v>3827</v>
       </c>
       <c r="L24" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="M24" t="s">
-        <v>3836</v>
+        <v>3828</v>
       </c>
       <c r="N24" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O24" t="s">
-        <v>3743</v>
+        <v>3735</v>
       </c>
       <c r="P24" t="n">
         <v>150114</v>
@@ -20255,33 +19888,33 @@
         <v>1740</v>
       </c>
       <c r="E25" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F25" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G25" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="K25" t="s">
-        <v>3837</v>
+        <v>3829</v>
       </c>
       <c r="L25" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="M25" t="s">
-        <v>3838</v>
+        <v>3830</v>
       </c>
       <c r="N25" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O25" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
       <c r="P25" t="n">
         <v>151906</v>
@@ -20301,30 +19934,30 @@
         <v>1140</v>
       </c>
       <c r="E26" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F26" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G26" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="K26" t="s">
-        <v>3839</v>
+        <v>3831</v>
       </c>
       <c r="L26" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="M26" t="s">
-        <v>3840</v>
+        <v>3832</v>
       </c>
       <c r="N26" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O26"/>
       <c r="P26" t="n">
@@ -20345,33 +19978,33 @@
         <v>1398</v>
       </c>
       <c r="E27" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F27" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G27" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3841</v>
+        <v>3833</v>
       </c>
       <c r="K27" t="s">
-        <v>3842</v>
+        <v>3834</v>
       </c>
       <c r="L27" t="s">
-        <v>3841</v>
+        <v>3833</v>
       </c>
       <c r="M27" t="s">
-        <v>3843</v>
+        <v>3835</v>
       </c>
       <c r="N27" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O27" t="s">
-        <v>3844</v>
+        <v>3836</v>
       </c>
       <c r="P27" t="n">
         <v>155314</v>
@@ -20391,33 +20024,33 @@
         <v>743</v>
       </c>
       <c r="E28" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F28" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G28" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3845</v>
+        <v>3837</v>
       </c>
       <c r="K28" t="s">
-        <v>3846</v>
+        <v>3838</v>
       </c>
       <c r="L28" t="s">
-        <v>3845</v>
+        <v>3837</v>
       </c>
       <c r="M28" t="s">
-        <v>3847</v>
+        <v>3839</v>
       </c>
       <c r="N28" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O28" t="s">
-        <v>3848</v>
+        <v>3840</v>
       </c>
       <c r="P28" t="n">
         <v>156914</v>
@@ -20437,13 +20070,13 @@
         <v>1191</v>
       </c>
       <c r="E29" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F29" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G29" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
@@ -20451,16 +20084,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s">
-        <v>3849</v>
+        <v>3841</v>
       </c>
       <c r="L29" t="s">
         <v>93</v>
       </c>
       <c r="M29" t="s">
-        <v>3850</v>
+        <v>3842</v>
       </c>
       <c r="N29" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O29" t="s">
         <v>94</v>
@@ -20483,33 +20116,33 @@
         <v>2694</v>
       </c>
       <c r="E30" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F30" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G30" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="K30" t="s">
-        <v>3851</v>
+        <v>3843</v>
       </c>
       <c r="L30" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="M30" t="s">
-        <v>3852</v>
+        <v>3844</v>
       </c>
       <c r="N30" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O30" t="s">
-        <v>3728</v>
+        <v>3720</v>
       </c>
       <c r="P30" t="n">
         <v>161412</v>
@@ -20529,33 +20162,33 @@
         <v>1683</v>
       </c>
       <c r="E31" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F31" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G31" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3729</v>
+        <v>3721</v>
       </c>
       <c r="K31" t="s">
-        <v>3853</v>
+        <v>3845</v>
       </c>
       <c r="L31" t="s">
-        <v>3729</v>
+        <v>3721</v>
       </c>
       <c r="M31" t="s">
-        <v>3854</v>
+        <v>3846</v>
       </c>
       <c r="N31" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O31" t="s">
-        <v>3730</v>
+        <v>3722</v>
       </c>
       <c r="P31" t="n">
         <v>164250</v>
@@ -20575,33 +20208,33 @@
         <v>3220</v>
       </c>
       <c r="E32" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F32" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G32" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3744</v>
+        <v>3736</v>
       </c>
       <c r="K32" t="s">
-        <v>3855</v>
+        <v>3847</v>
       </c>
       <c r="L32" t="s">
-        <v>3744</v>
+        <v>3736</v>
       </c>
       <c r="M32" t="s">
-        <v>3856</v>
+        <v>3848</v>
       </c>
       <c r="N32" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O32" t="s">
-        <v>3746</v>
+        <v>3738</v>
       </c>
       <c r="P32" t="n">
         <v>168962</v>
@@ -20621,30 +20254,30 @@
         <v>1665</v>
       </c>
       <c r="E33" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F33" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G33" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="K33" t="s">
-        <v>3857</v>
+        <v>3849</v>
       </c>
       <c r="L33" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="M33" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N33" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O33"/>
       <c r="P33" t="n">
@@ -20665,33 +20298,33 @@
         <v>1038</v>
       </c>
       <c r="E34" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F34" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G34" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3858</v>
+        <v>3850</v>
       </c>
       <c r="K34" t="s">
-        <v>3859</v>
+        <v>3851</v>
       </c>
       <c r="L34" t="s">
-        <v>3858</v>
+        <v>3850</v>
       </c>
       <c r="M34" t="s">
-        <v>3860</v>
+        <v>3852</v>
       </c>
       <c r="N34" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O34" t="s">
-        <v>3861</v>
+        <v>3853</v>
       </c>
       <c r="P34" t="n">
         <v>173804</v>
@@ -20711,33 +20344,33 @@
         <v>801</v>
       </c>
       <c r="E35" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F35" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G35" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3723</v>
+        <v>3715</v>
       </c>
       <c r="K35" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
       <c r="L35" t="s">
-        <v>3723</v>
+        <v>3715</v>
       </c>
       <c r="M35" t="s">
-        <v>3863</v>
+        <v>3855</v>
       </c>
       <c r="N35" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O35" t="s">
-        <v>3724</v>
+        <v>3716</v>
       </c>
       <c r="P35" t="n">
         <v>174945</v>
@@ -20757,33 +20390,33 @@
         <v>4587</v>
       </c>
       <c r="E36" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F36" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G36" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3753</v>
+        <v>3745</v>
       </c>
       <c r="K36" t="s">
-        <v>3864</v>
+        <v>3856</v>
       </c>
       <c r="L36" t="s">
-        <v>3753</v>
+        <v>3745</v>
       </c>
       <c r="M36" t="s">
-        <v>3865</v>
+        <v>3857</v>
       </c>
       <c r="N36" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O36" t="s">
-        <v>3755</v>
+        <v>3747</v>
       </c>
       <c r="P36" t="n">
         <v>177820</v>
@@ -20803,33 +20436,33 @@
         <v>1419</v>
       </c>
       <c r="E37" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F37" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G37" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3866</v>
+        <v>3858</v>
       </c>
       <c r="K37" t="s">
-        <v>3867</v>
+        <v>3859</v>
       </c>
       <c r="L37" t="s">
-        <v>3866</v>
+        <v>3858</v>
       </c>
       <c r="M37" t="s">
-        <v>3868</v>
+        <v>3860</v>
       </c>
       <c r="N37" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O37" t="s">
-        <v>3869</v>
+        <v>3861</v>
       </c>
       <c r="P37" t="n">
         <v>181409</v>
@@ -20849,33 +20482,33 @@
         <v>1695</v>
       </c>
       <c r="E38" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F38" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G38" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3870</v>
+        <v>3862</v>
       </c>
       <c r="K38" t="s">
-        <v>3871</v>
+        <v>3863</v>
       </c>
       <c r="L38" t="s">
-        <v>3870</v>
+        <v>3862</v>
       </c>
       <c r="M38" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
       <c r="N38" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O38" t="s">
-        <v>3873</v>
+        <v>3865</v>
       </c>
       <c r="P38" t="n">
         <v>183237</v>
@@ -20895,33 +20528,33 @@
         <v>1242</v>
       </c>
       <c r="E39" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F39" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G39" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>3874</v>
+        <v>3866</v>
       </c>
       <c r="K39" t="s">
-        <v>3875</v>
+        <v>3867</v>
       </c>
       <c r="L39" t="s">
-        <v>3874</v>
+        <v>3866</v>
       </c>
       <c r="M39" t="s">
-        <v>3876</v>
+        <v>3868</v>
       </c>
       <c r="N39" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O39" t="s">
-        <v>3877</v>
+        <v>3869</v>
       </c>
       <c r="P39" t="n">
         <v>184774</v>
@@ -20941,33 +20574,33 @@
         <v>1281</v>
       </c>
       <c r="E40" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F40" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G40" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>3719</v>
+        <v>3711</v>
       </c>
       <c r="K40" t="s">
-        <v>3878</v>
+        <v>3870</v>
       </c>
       <c r="L40" t="s">
-        <v>3719</v>
+        <v>3711</v>
       </c>
       <c r="M40" t="s">
-        <v>3879</v>
+        <v>3871</v>
       </c>
       <c r="N40" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O40" t="s">
-        <v>3720</v>
+        <v>3712</v>
       </c>
       <c r="P40" t="n">
         <v>186699</v>
@@ -20987,33 +20620,33 @@
         <v>333</v>
       </c>
       <c r="E41" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F41" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G41" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>3880</v>
+        <v>3872</v>
       </c>
       <c r="K41" t="s">
-        <v>3881</v>
+        <v>3873</v>
       </c>
       <c r="L41" t="s">
-        <v>3880</v>
+        <v>3872</v>
       </c>
       <c r="M41" t="s">
-        <v>3791</v>
+        <v>3783</v>
       </c>
       <c r="N41" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O41" t="s">
-        <v>3882</v>
+        <v>3874</v>
       </c>
       <c r="P41" t="n">
         <v>187630</v>
@@ -21033,33 +20666,33 @@
         <v>2853</v>
       </c>
       <c r="E42" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F42" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G42" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>3883</v>
+        <v>3875</v>
       </c>
       <c r="K42" t="s">
-        <v>3884</v>
+        <v>3876</v>
       </c>
       <c r="L42" t="s">
-        <v>3883</v>
+        <v>3875</v>
       </c>
       <c r="M42" t="s">
-        <v>3885</v>
+        <v>3877</v>
       </c>
       <c r="N42" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O42" t="s">
-        <v>3886</v>
+        <v>3878</v>
       </c>
       <c r="P42" t="n">
         <v>189042</v>
@@ -21079,33 +20712,33 @@
         <v>678</v>
       </c>
       <c r="E43" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F43" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G43" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>3887</v>
+        <v>3879</v>
       </c>
       <c r="K43" t="s">
-        <v>3888</v>
+        <v>3880</v>
       </c>
       <c r="L43" t="s">
-        <v>3887</v>
+        <v>3879</v>
       </c>
       <c r="M43" t="s">
-        <v>3889</v>
+        <v>3881</v>
       </c>
       <c r="N43" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O43" t="s">
-        <v>3890</v>
+        <v>3882</v>
       </c>
       <c r="P43" t="n">
         <v>191468</v>
@@ -21125,33 +20758,33 @@
         <v>1323</v>
       </c>
       <c r="E44" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F44" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G44" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>3891</v>
+        <v>3883</v>
       </c>
       <c r="K44" t="s">
-        <v>3892</v>
+        <v>3884</v>
       </c>
       <c r="L44" t="s">
-        <v>3891</v>
+        <v>3883</v>
       </c>
       <c r="M44" t="s">
-        <v>3893</v>
+        <v>3885</v>
       </c>
       <c r="N44" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O44" t="s">
-        <v>3894</v>
+        <v>3886</v>
       </c>
       <c r="P44" t="n">
         <v>192639</v>
@@ -21171,33 +20804,33 @@
         <v>2697</v>
       </c>
       <c r="E45" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F45" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G45" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>3895</v>
+        <v>3887</v>
       </c>
       <c r="K45" t="s">
-        <v>3896</v>
+        <v>3888</v>
       </c>
       <c r="L45" t="s">
-        <v>3895</v>
+        <v>3887</v>
       </c>
       <c r="M45" t="s">
-        <v>3897</v>
+        <v>3889</v>
       </c>
       <c r="N45" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O45" t="s">
-        <v>3898</v>
+        <v>3890</v>
       </c>
       <c r="P45" t="n">
         <v>195055</v>
@@ -21217,33 +20850,33 @@
         <v>900</v>
       </c>
       <c r="E46" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F46" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G46" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>3899</v>
+        <v>3891</v>
       </c>
       <c r="K46" t="s">
-        <v>3900</v>
+        <v>3892</v>
       </c>
       <c r="L46" t="s">
-        <v>3899</v>
+        <v>3891</v>
       </c>
       <c r="M46" t="s">
-        <v>3901</v>
+        <v>3893</v>
       </c>
       <c r="N46" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O46" t="s">
-        <v>3902</v>
+        <v>3894</v>
       </c>
       <c r="P46" t="n">
         <v>198588</v>
@@ -21263,33 +20896,33 @@
         <v>933</v>
       </c>
       <c r="E47" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="F47" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G47" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
       <c r="K47" t="s">
-        <v>3903</v>
+        <v>3895</v>
       </c>
       <c r="L47" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
       <c r="M47" t="s">
-        <v>3807</v>
+        <v>3799</v>
       </c>
       <c r="N47" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O47" t="s">
-        <v>3707</v>
+        <v>3699</v>
       </c>
       <c r="P47" t="n">
         <v>199676</v>
@@ -21309,33 +20942,33 @@
         <v>1713</v>
       </c>
       <c r="E48" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F48" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G48" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>3904</v>
+        <v>3896</v>
       </c>
       <c r="K48" t="s">
-        <v>3905</v>
+        <v>3897</v>
       </c>
       <c r="L48" t="s">
-        <v>3904</v>
+        <v>3896</v>
       </c>
       <c r="M48" t="s">
-        <v>3906</v>
+        <v>3898</v>
       </c>
       <c r="N48" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O48" t="s">
-        <v>3907</v>
+        <v>3899</v>
       </c>
       <c r="P48" t="n">
         <v>201417</v>
@@ -21355,30 +20988,30 @@
         <v>1113</v>
       </c>
       <c r="E49" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F49" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G49" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>3908</v>
+        <v>3900</v>
       </c>
       <c r="K49" t="s">
-        <v>3909</v>
+        <v>3901</v>
       </c>
       <c r="L49" t="s">
-        <v>3908</v>
+        <v>3900</v>
       </c>
       <c r="M49" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N49" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="O49"/>
       <c r="P49" t="n">
@@ -21399,33 +21032,33 @@
         <v>1539</v>
       </c>
       <c r="E50" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F50" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G50" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>3910</v>
+        <v>3902</v>
       </c>
       <c r="K50" t="s">
-        <v>3911</v>
+        <v>3903</v>
       </c>
       <c r="L50" t="s">
-        <v>3910</v>
+        <v>3902</v>
       </c>
       <c r="M50" t="s">
-        <v>3912</v>
+        <v>3904</v>
       </c>
       <c r="N50" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O50" t="s">
-        <v>3913</v>
+        <v>3905</v>
       </c>
       <c r="P50" t="n">
         <v>207802</v>
@@ -21445,33 +21078,33 @@
         <v>1044</v>
       </c>
       <c r="E51" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F51" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G51" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="K51" t="s">
-        <v>3914</v>
+        <v>3906</v>
       </c>
       <c r="L51" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="M51" t="s">
-        <v>3915</v>
+        <v>3907</v>
       </c>
       <c r="N51" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O51" t="s">
-        <v>3715</v>
+        <v>3707</v>
       </c>
       <c r="P51" t="n">
         <v>209528</v>
@@ -21491,33 +21124,33 @@
         <v>3252</v>
       </c>
       <c r="E52" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F52" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G52" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52" t="s">
-        <v>3756</v>
+        <v>3748</v>
       </c>
       <c r="K52" t="s">
-        <v>3916</v>
+        <v>3908</v>
       </c>
       <c r="L52" t="s">
-        <v>3756</v>
+        <v>3748</v>
       </c>
       <c r="M52" t="s">
-        <v>3917</v>
+        <v>3909</v>
       </c>
       <c r="N52" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O52" t="s">
-        <v>3758</v>
+        <v>3750</v>
       </c>
       <c r="P52" t="n">
         <v>212042</v>
@@ -21537,33 +21170,33 @@
         <v>1131</v>
       </c>
       <c r="E53" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="F53" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="G53" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="H53"/>
       <c r="I53"/>
       <c r="J53" t="s">
-        <v>3918</v>
+        <v>3910</v>
       </c>
       <c r="K53" t="s">
-        <v>3919</v>
+        <v>3911</v>
       </c>
       <c r="L53" t="s">
-        <v>3918</v>
+        <v>3910</v>
       </c>
       <c r="M53" t="s">
-        <v>3920</v>
+        <v>3912</v>
       </c>
       <c r="N53" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="O53" t="s">
-        <v>3921</v>
+        <v>3913</v>
       </c>
       <c r="P53" t="n">
         <v>214646</v>
@@ -72272,10 +71905,10 @@
         <v>0.000127560374248132</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00497485459567715</v>
+        <v>0.00510241496992528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00416249642283378</v>
+        <v>0.00429677050098971</v>
       </c>
       <c r="J2" t="s">
         <v>2128</v>
@@ -72307,10 +71940,10 @@
         <v>0.000520536027926073</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0101504525445584</v>
+        <v>0.0104107205585215</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00849295624510961</v>
+        <v>0.00876692257559702</v>
       </c>
       <c r="J3" t="s">
         <v>2133</v>
